--- a/CMAM-Lote-2-Atualizado-Feito.xlsx
+++ b/CMAM-Lote-2-Atualizado-Feito.xlsx
@@ -1,238 +1,142 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wilson\Desktop\CMAM Concurso\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Nº0016" sheetId="1" r:id="rId1"/>
+    <sheet name="Nº0016" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_Toc68319419" localSheetId="0">Nº0016!#REF!</definedName>
     <definedName name="_Toc68319420" localSheetId="0">Nº0016!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Nº0016!$A$1:$J$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">Nº0016!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Nº0016'!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Nº0016'!$A$1:$J$17</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
-  <si>
-    <t>Endereço: Rua da França, N°273, Bairro da Coop</t>
-  </si>
-  <si>
-    <t>Email: info@infinityhealth.co.mz</t>
-  </si>
-  <si>
-    <t>Telef: +258 86 226 0072</t>
-  </si>
-  <si>
-    <t>NUIT 401550216</t>
-  </si>
-  <si>
-    <t>Maputo - Moçambique</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descrição dos Bens </t>
-  </si>
-  <si>
-    <t>País de Origem</t>
-  </si>
-  <si>
-    <t>Tempo De Entrega</t>
-  </si>
-  <si>
-    <t>QTD</t>
-  </si>
-  <si>
-    <t>Unidade Física</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preço Unitário </t>
-  </si>
-  <si>
-    <t>Preço Total s/IVA</t>
-  </si>
-  <si>
-    <t>IVA 16%</t>
-  </si>
-  <si>
-    <t>Preço Total c/IVA</t>
-  </si>
-  <si>
-    <t>UN</t>
-  </si>
-  <si>
-    <t>Contratação de fornecimento de material médico cirúrgico de grande rotação (Equipamentos de Proteção Individual) para o SNS</t>
-  </si>
-  <si>
-    <t>Concurso Público Nº 58A001241/CP/03/OE – Material Médico-Cirúrgicos de Grande Rotação/026</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>90 Dias Úteis</t>
-  </si>
-  <si>
-    <t>Preço Total Com IVA em USD</t>
-  </si>
-  <si>
-    <t>Cambio:1USD-63,89MT</t>
-  </si>
-  <si>
-    <t>Bata descartável tamanho M (TNT polipropileno, punho elástico)</t>
-  </si>
-  <si>
-    <t>Bata descartável tamanho S (TNT polipropileno, punho elástico)</t>
-  </si>
-  <si>
-    <t>Bata cirúrgica reforçada descartável, estéril, tamanho M (SMS/SMMS)</t>
-  </si>
-  <si>
-    <t>Bata cirúrgica reforçada descartável, estéril, tamanho L (SMS/SMMS)
-un</t>
-  </si>
-  <si>
-    <t>Bata cirúrgica reforçada descartável, estéril, tamanho XL (SMS/SMMS)</t>
-  </si>
-  <si>
-    <t>Lote 2 - Material de Proteção Individual - Bata descartável</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="8"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color indexed="8"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial Nova Light"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Arial Nova Light"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -588,268 +492,369 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="98">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="11"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1593215</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>160021</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>30480</colOff>
+      <row>1</row>
+      <rowOff>38101</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>1593215</colOff>
+      <row>2</row>
+      <rowOff>160021</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm>
           <a:off x="30480" y="419101"/>
           <a:ext cx="1882140" cy="624840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1138,489 +1143,568 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="2" max="2" width="55.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="20" style="49" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" hidden="1" customWidth="1"/>
+    <col width="4.140625" customWidth="1" style="71" min="1" max="1"/>
+    <col width="55.140625" customWidth="1" style="71" min="2" max="2"/>
+    <col width="10.42578125" customWidth="1" style="71" min="3" max="3"/>
+    <col width="12.7109375" customWidth="1" style="71" min="4" max="4"/>
+    <col width="20.140625" customWidth="1" style="71" min="5" max="5"/>
+    <col width="7.85546875" customWidth="1" style="71" min="6" max="6"/>
+    <col width="14" customWidth="1" style="71" min="7" max="7"/>
+    <col width="17.85546875" customWidth="1" style="71" min="8" max="8"/>
+    <col width="15.140625" customWidth="1" style="71" min="9" max="9"/>
+    <col width="20" customWidth="1" style="71" min="10" max="10"/>
+    <col width="20" customWidth="1" style="71" min="11" max="11"/>
+    <col width="8.140625" customWidth="1" style="71" min="12" max="12"/>
+    <col hidden="1" width="8.85546875" customWidth="1" style="71" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="53"/>
-      <c r="M1" s="6">
+    <row r="1" ht="30" customHeight="1" s="71" thickBot="1" thickTop="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>Contratação de fornecimento de material médico cirúrgico de grande rotação (Equipamentos de Proteção Individual) para o SNS</t>
+        </is>
+      </c>
+      <c r="B1" s="66" t="n"/>
+      <c r="C1" s="66" t="n"/>
+      <c r="D1" s="66" t="n"/>
+      <c r="E1" s="66" t="n"/>
+      <c r="F1" s="66" t="n"/>
+      <c r="G1" s="66" t="n"/>
+      <c r="H1" s="66" t="n"/>
+      <c r="I1" s="66" t="n"/>
+      <c r="J1" s="66" t="n"/>
+      <c r="M1" s="6" t="n">
         <v>0.16</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="75"/>
-      <c r="M2" s="6">
+    <row r="2" ht="39.95" customHeight="1" s="71" thickTop="1">
+      <c r="A2" s="72" t="n"/>
+      <c r="B2" s="73" t="n"/>
+      <c r="C2" s="73" t="n"/>
+      <c r="D2" s="73" t="n"/>
+      <c r="E2" s="73" t="n"/>
+      <c r="F2" s="73" t="n"/>
+      <c r="G2" s="75" t="inlineStr">
+        <is>
+          <t>Concurso Público Nº 58A001241/CP/03/OE – Material Médico-Cirúrgicos de Grande Rotação/026</t>
+        </is>
+      </c>
+      <c r="H2" s="73" t="n"/>
+      <c r="I2" s="73" t="n"/>
+      <c r="J2" s="73" t="n"/>
+      <c r="K2" s="78" t="n"/>
+      <c r="M2" s="6" t="n">
         <v>0.16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="25"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:15" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+    <row r="3" ht="24.6" customHeight="1" s="71">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Endereço: Rua da França, N°273, Bairro da Coop</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="35" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="M3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="16.35" customHeight="1" s="71">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Email: info@infinityhealth.co.mz</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="35" t="n"/>
+      <c r="E4" s="35" t="n"/>
+      <c r="F4" s="35" t="n"/>
+      <c r="G4" s="35" t="n"/>
+      <c r="H4" s="35" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="16.35" customHeight="1" s="71">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Telef: +258 86 226 0072</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="70" t="inlineStr">
+        <is>
+          <t>Lote 2 - Material de Proteção Individual - Bata descartável</t>
+        </is>
+      </c>
+      <c r="J5" s="77" t="inlineStr">
+        <is>
+          <t>Cambio:1USD-63,89MT</t>
+        </is>
+      </c>
+      <c r="K5" s="61" t="n"/>
+      <c r="O5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="14.45" customHeight="1" s="71">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>NUIT 401550216</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="55" t="n"/>
+      <c r="J6" s="55" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="O6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="13.35" customHeight="1" s="71">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Maputo - Moçambique</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="55" t="n"/>
+      <c r="J7" s="55" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="O7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" s="71" thickBot="1">
+      <c r="A8" s="79" t="n"/>
+      <c r="B8" s="68" t="n"/>
+      <c r="C8" s="68" t="n"/>
+      <c r="D8" s="80" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="69" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="68" t="n"/>
+      <c r="J8" s="81" t="n"/>
+      <c r="K8" s="61" t="n"/>
+      <c r="O8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1" thickTop="1">
+      <c r="A9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="25"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:15" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="B9" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="77"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="C9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="20"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="20"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="67"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="61"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
-        <v>1</v>
-      </c>
-      <c r="B9" s="11">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11">
-        <v>3</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11">
-        <v>4</v>
-      </c>
-      <c r="F9" s="11">
+      <c r="F9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="K9" s="62">
+      <c r="K9" s="62" t="n">
         <v>10</v>
       </c>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="15" t="s">
+      <c r="L9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="26.25" customHeight="1" s="71" thickBot="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descrição dos Bens </t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>País de Origem</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Tempo De Entrega</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>QTD</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Unidade Física</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preço Unitário </t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Preço Total s/IVA</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>IVA 16%</t>
+        </is>
+      </c>
+      <c r="J10" s="60" t="inlineStr">
+        <is>
+          <t>Preço Total c/IVA</t>
+        </is>
+      </c>
+      <c r="K10" s="56" t="inlineStr">
+        <is>
+          <t>Preço Total Com IVA em USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27.95" customFormat="1" customHeight="1" s="36">
+      <c r="A11" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Bata descartável tamanho M (TNT polipropileno, punho elástico)</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t>90 Dias Úteis</t>
+        </is>
+      </c>
+      <c r="E11" s="82" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F11" s="39" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G11" s="83" t="n">
+        <v>85</v>
+      </c>
+      <c r="H11" s="83">
+        <f>+G11*E11</f>
+        <v/>
+      </c>
+      <c r="I11" s="84">
+        <f>+H11*16%</f>
+        <v/>
+      </c>
+      <c r="J11" s="85">
+        <f>I11+H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="86">
+        <f>+J11/63.89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="32.1" customHeight="1" s="71">
+      <c r="A12" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Bata descartável tamanho S (TNT polipropileno, punho elástico)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>90 Dias Úteis</t>
+        </is>
+      </c>
+      <c r="E12" s="87" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G12" s="88" t="n">
+        <v>85</v>
+      </c>
+      <c r="H12" s="88">
+        <f>+G12*E12</f>
+        <v/>
+      </c>
+      <c r="I12" s="89">
+        <f>16%*H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="89">
+        <f>I12+H12</f>
+        <v/>
+      </c>
+      <c r="K12" s="90">
+        <f>+J12/63.89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" s="71">
+      <c r="A13" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Bata cirúrgica reforçada descartável, estéril, tamanho M (SMS/SMMS)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>90 Dias Úteis</t>
+        </is>
+      </c>
+      <c r="E13" s="87" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G13" s="88" t="n">
+        <v>130</v>
+      </c>
+      <c r="H13" s="88">
+        <f>+G13*E13</f>
+        <v/>
+      </c>
+      <c r="I13" s="89">
+        <f>+H13*16%</f>
+        <v/>
+      </c>
+      <c r="J13" s="89">
+        <f>I13+H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="90">
+        <f>+J13/63.89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="31.5" customHeight="1" s="71">
+      <c r="A14" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Bata cirúrgica reforçada descartável, estéril, tamanho L (SMS/SMMS)
+un</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>90 Dias Úteis</t>
+        </is>
+      </c>
+      <c r="E14" s="87" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G14" s="88" t="n">
+        <v>130</v>
+      </c>
+      <c r="H14" s="88">
+        <f>+G14*E14</f>
+        <v/>
+      </c>
+      <c r="I14" s="89">
+        <f>+H14*16%</f>
+        <v/>
+      </c>
+      <c r="J14" s="89">
+        <f>I14+H14</f>
+        <v/>
+      </c>
+      <c r="K14" s="90">
+        <f>+J14/63.89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="47.25" customHeight="1" s="71" thickBot="1">
+      <c r="A15" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="I10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="56" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" s="36" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37">
-        <v>8</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="51">
-        <v>100000</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="41">
-        <v>125</v>
-      </c>
-      <c r="H11" s="41">
-        <f t="shared" ref="H11:H15" si="0">+G11*E11</f>
-        <v>12500000</v>
-      </c>
-      <c r="I11" s="42">
-        <f>+H11*16%</f>
-        <v>2000000</v>
-      </c>
-      <c r="J11" s="59">
-        <f t="shared" ref="J11:J15" si="1">I11+H11</f>
-        <v>14500000</v>
-      </c>
-      <c r="K11" s="63">
-        <f>+J11/63.89</f>
-        <v>226952.57473783064</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
-        <v>9</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="50">
-        <v>100000</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="43">
-        <v>125</v>
-      </c>
-      <c r="H12" s="43">
-        <f t="shared" si="0"/>
-        <v>12500000</v>
-      </c>
-      <c r="I12" s="44">
-        <f>16%*H12</f>
-        <v>2000000</v>
-      </c>
-      <c r="J12" s="44">
-        <f t="shared" si="1"/>
-        <v>14500000</v>
-      </c>
-      <c r="K12" s="64">
-        <f>+J12/63.89</f>
-        <v>226952.57473783064</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
-        <v>10</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="50">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Bata cirúrgica reforçada descartável, estéril, tamanho XL (SMS/SMMS)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>90 Dias Úteis</t>
+        </is>
+      </c>
+      <c r="E15" s="91" t="n">
         <v>600000</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="43">
-        <v>125</v>
-      </c>
-      <c r="H13" s="43">
-        <f t="shared" si="0"/>
-        <v>75000000</v>
-      </c>
-      <c r="I13" s="44">
-        <f t="shared" ref="I13:I15" si="2">+H13*16%</f>
-        <v>12000000</v>
-      </c>
-      <c r="J13" s="44">
-        <f t="shared" si="1"/>
-        <v>87000000</v>
-      </c>
-      <c r="K13" s="64">
-        <f>+J13/63.89</f>
-        <v>1361715.4484269838</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
-        <v>11</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="50">
-        <v>600000</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="43">
-        <v>3</v>
-      </c>
-      <c r="H14" s="43">
-        <f t="shared" si="0"/>
-        <v>1800000</v>
-      </c>
-      <c r="I14" s="44">
-        <f t="shared" si="2"/>
-        <v>288000</v>
-      </c>
-      <c r="J14" s="44">
-        <f t="shared" si="1"/>
-        <v>2088000</v>
-      </c>
-      <c r="K14" s="64">
-        <f>+J14/63.89</f>
-        <v>32681.170762247613</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18">
-        <v>12</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="52">
-        <v>600000</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="43">
-        <v>235</v>
-      </c>
-      <c r="H15" s="43">
-        <f t="shared" si="0"/>
-        <v>141000000</v>
-      </c>
-      <c r="I15" s="44">
-        <f t="shared" si="2"/>
-        <v>22560000</v>
-      </c>
-      <c r="J15" s="44">
-        <f t="shared" si="1"/>
-        <v>163560000</v>
-      </c>
-      <c r="K15" s="64">
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="G15" s="88" t="n">
+        <v>130</v>
+      </c>
+      <c r="H15" s="88">
+        <f>+G15*E15</f>
+        <v/>
+      </c>
+      <c r="I15" s="89">
+        <f>+H15*16%</f>
+        <v/>
+      </c>
+      <c r="J15" s="89">
+        <f>I15+H15</f>
+        <v/>
+      </c>
+      <c r="K15" s="90">
         <f>+J15/63.89</f>
-        <v>2560025.0430427296</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="17.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="45">
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="17.25" customHeight="1" s="71" thickBot="1" thickTop="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="92">
         <f>SUM(H11:H15)</f>
-        <v>242800000</v>
-      </c>
-      <c r="I16" s="46">
+        <v/>
+      </c>
+      <c r="I16" s="93">
         <f>SUM(I11:I15)</f>
-        <v>38848000</v>
-      </c>
-      <c r="J16" s="58">
+        <v/>
+      </c>
+      <c r="J16" s="94">
         <f>SUM(J11:J15)</f>
-        <v>281648000</v>
-      </c>
-      <c r="K16" s="57">
+        <v/>
+      </c>
+      <c r="K16" s="95">
         <f>SUM(K11:K15)</f>
-        <v>4408326.8117076224</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
-      <c r="I18" s="48"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1" s="71" thickTop="1">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="96" t="n"/>
+      <c r="K17" s="96" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="16" t="n"/>
+      <c r="I18" s="97" t="n"/>
+    </row>
+    <row r="19">
+      <c r="H19" s="97" t="n"/>
+      <c r="J19" s="97" t="n"/>
+      <c r="K19" s="97" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="G2:K2"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" display="info@infinityhealth.co.mz"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" display="info@infinityhealth.co.mz" r:id="rId1"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.51181102362204722" right="0.59055118110236227" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
-  <pageSetup scale="70" orientation="landscape"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.5118110236220472" right="0.5905511811023623" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageSetup orientation="landscape" scale="70"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>